--- a/OUTPUT/gate_oof/fold_0/expert_inner_metrics.xlsx
+++ b/OUTPUT/gate_oof/fold_0/expert_inner_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,10 +535,10 @@
         <v>460</v>
       </c>
       <c r="H2" t="n">
-        <v>2.349927699999171</v>
+        <v>2.59768109995639</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02993059999971592</v>
+        <v>0.02317060000495985</v>
       </c>
       <c r="J2" t="n">
         <v>0.00374102819563021</v>
@@ -587,31 +587,31 @@
         <v>752</v>
       </c>
       <c r="H3" t="n">
-        <v>4.713378700000249</v>
+        <v>5.867028100008611</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3960516999995889</v>
+        <v>0.5041393999708816</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005954584914467914</v>
+        <v>0.005969693429504489</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004173641154875581</v>
+        <v>0.004184076376289426</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6769734299850465</v>
+        <v>0.6753321255368572</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4352033787751822</v>
+        <v>0.4362867627978259</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.835248750119439e-05</v>
+        <v>-6.323158856782956e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01257092455823497</v>
+        <v>0.01250982256443249</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02526976408411852</v>
+        <v>0.02547894883386304</v>
       </c>
     </row>
     <row r="4">
@@ -639,31 +639,31 @@
         <v>1443</v>
       </c>
       <c r="H4" t="n">
-        <v>8.837089900000137</v>
+        <v>32.78647800005274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3717000000015105</v>
+        <v>2.071898300026078</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005362746335361327</v>
+        <v>0.005363191219384994</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00416123196585681</v>
+        <v>0.004164665800768361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6032232033886611</v>
+        <v>0.6031573688447107</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4218107525636371</v>
+        <v>0.4221582805392162</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.855161188639668e-05</v>
+        <v>-4.081591508791544e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01099903353620068</v>
+        <v>0.01091370209192181</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01897213825407129</v>
+        <v>0.0192852281069682</v>
       </c>
     </row>
     <row r="5">
@@ -691,10 +691,10 @@
         <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8925263000001</v>
+        <v>8.484886399994139</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02981809999982943</v>
+        <v>0.09684559999732301</v>
       </c>
       <c r="J5" t="n">
         <v>0.003879451280083577</v>
@@ -743,31 +743,31 @@
         <v>752</v>
       </c>
       <c r="H6" t="n">
-        <v>4.838048499999786</v>
+        <v>16.79323890001979</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4251419000011083</v>
+        <v>0.2872377999592572</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005412912675277964</v>
+        <v>0.005398407101013785</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00387930959817846</v>
+        <v>0.003867443071365255</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7301745965546984</v>
+        <v>0.7316188201409534</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4039252566731123</v>
+        <v>0.4026757854566912</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0003635984025323027</v>
+        <v>-0.0003700794637270638</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01131555082628069</v>
+        <v>0.01146352413068201</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02404902510289153</v>
+        <v>0.023939124802274</v>
       </c>
     </row>
     <row r="7">
@@ -795,31 +795,31 @@
         <v>1442</v>
       </c>
       <c r="H7" t="n">
-        <v>8.807227000001149</v>
+        <v>6.521616699988954</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3852154999985942</v>
+        <v>0.2603434000047855</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005581030358580088</v>
+        <v>0.005580945665005125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004224357040422495</v>
+        <v>0.004232428370631814</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5766816960214758</v>
+        <v>0.5766945438528521</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4282041097592442</v>
+        <v>0.429032430427848</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.428667019038997e-05</v>
+        <v>-1.383097805917295e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01159000547231531</v>
+        <v>0.01157998684291629</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02280286451224001</v>
+        <v>0.02306938610653841</v>
       </c>
     </row>
     <row r="8">
@@ -847,10 +847,10 @@
         <v>460</v>
       </c>
       <c r="H8" t="n">
-        <v>2.391717299999073</v>
+        <v>5.010116799967363</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03371419999893988</v>
+        <v>0.1015718000126071</v>
       </c>
       <c r="J8" t="n">
         <v>0.00372536995965931</v>
@@ -899,31 +899,31 @@
         <v>751</v>
       </c>
       <c r="H9" t="n">
-        <v>4.823531100000764</v>
+        <v>30.16057040001033</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4233320000003005</v>
+        <v>1.677270299987867</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005595615039243479</v>
+        <v>0.005589002886847066</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004059253370756263</v>
+        <v>0.00404277014472521</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7135987217020086</v>
+        <v>0.7142751835411798</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4226491951590132</v>
+        <v>0.4209194216614938</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0004506583721678771</v>
+        <v>-0.0004649436695049525</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01186048797599659</v>
+        <v>0.01178374509721913</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01950605724198573</v>
+        <v>0.01971576817176968</v>
       </c>
     </row>
     <row r="10">
@@ -951,31 +951,31 @@
         <v>1442</v>
       </c>
       <c r="H10" t="n">
-        <v>10.85167659999934</v>
+        <v>40.11289849999594</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5452513999989606</v>
+        <v>0.3188109999755397</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005392594129830855</v>
+        <v>0.005386416439989329</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004109409158835911</v>
+        <v>0.004105539398738601</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6010732474106206</v>
+        <v>0.6019867350821348</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4167578239670605</v>
+        <v>0.4163717588562548</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0001225855058600171</v>
+        <v>0.0001253737854297882</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01090441934078823</v>
+        <v>0.01088827269870129</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0200905454749073</v>
+        <v>0.02004499592674736</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         <v>460</v>
       </c>
       <c r="H11" t="n">
-        <v>3.182203300000765</v>
+        <v>1.262115099991206</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0377903000007791</v>
+        <v>0.01526120002381504</v>
       </c>
       <c r="J11" t="n">
         <v>0.003491239073353557</v>
@@ -1055,31 +1055,31 @@
         <v>751</v>
       </c>
       <c r="H12" t="n">
-        <v>9.227302999999665</v>
+        <v>3.828130300040357</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5879512999999861</v>
+        <v>0.4061737000010908</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005075719444799857</v>
+        <v>0.005079927001950732</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003658031095045798</v>
+        <v>0.003663979339994349</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7612341525762109</v>
+        <v>0.7608381348869665</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3812876179133934</v>
+        <v>0.3819028589373604</v>
       </c>
       <c r="N12" t="n">
-        <v>0.000109206507882964</v>
+        <v>0.0001013060033412768</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01084981054386464</v>
+        <v>0.01063922254652921</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0188745557177703</v>
+        <v>0.01896397185355558</v>
       </c>
     </row>
     <row r="13">
@@ -1107,31 +1107,31 @@
         <v>1442</v>
       </c>
       <c r="H13" t="n">
-        <v>13.43311949999952</v>
+        <v>6.424260200001299</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4634645999994973</v>
+        <v>0.2628679000190459</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00536209084720465</v>
+        <v>0.005362413459208139</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004100060658986267</v>
+        <v>0.004102477861607283</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6042904504384492</v>
+        <v>0.6042428330091312</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4155942300467572</v>
+        <v>0.415840224459572</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.128966800162339e-05</v>
+        <v>-6.541935477158142e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01121957699163334</v>
+        <v>0.01123217136595288</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01830667641943629</v>
+        <v>0.01814139128259984</v>
       </c>
     </row>
     <row r="14">
@@ -1159,10 +1159,10 @@
         <v>460</v>
       </c>
       <c r="H14" t="n">
-        <v>2.156283000000258</v>
+        <v>1.109340599970892</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0259635000002163</v>
+        <v>0.01745470002060756</v>
       </c>
       <c r="J14" t="n">
         <v>0.003646913592111171</v>
@@ -1211,31 +1211,31 @@
         <v>752</v>
       </c>
       <c r="H15" t="n">
-        <v>5.569662399999288</v>
+        <v>3.52313609997509</v>
       </c>
       <c r="I15" t="n">
-        <v>0.447226899999805</v>
+        <v>0.3354590000235476</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005548062793586654</v>
+        <v>0.005523358257333006</v>
       </c>
       <c r="K15" t="n">
-        <v>0.003995892252154703</v>
+        <v>0.003972248087529676</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7192151458225096</v>
+        <v>0.7217101484970027</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4160471813600153</v>
+        <v>0.4135879783425316</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0004429885455478016</v>
+        <v>-0.0004464769013348629</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01135875061496579</v>
+        <v>0.01143742365986514</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02168040742639954</v>
+        <v>0.02144283260258584</v>
       </c>
     </row>
     <row r="16">
@@ -1263,31 +1263,31 @@
         <v>1442</v>
       </c>
       <c r="H16" t="n">
-        <v>10.32884120000017</v>
+        <v>6.500193900021259</v>
       </c>
       <c r="I16" t="n">
-        <v>0.451342400001522</v>
+        <v>0.279463900020346</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005368567588712724</v>
+        <v>0.005372078357577814</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004089069646606222</v>
+        <v>0.004087721391100519</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6023370035359394</v>
+        <v>0.6018167309180862</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4146837868152398</v>
+        <v>0.414550337434212</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0002059307630797621</v>
+        <v>0.0002157483773764068</v>
       </c>
       <c r="O16" t="n">
-        <v>0.011223059801857</v>
+        <v>0.01130021309523806</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02070904282586983</v>
+        <v>0.02131687467346133</v>
       </c>
     </row>
   </sheetData>
